--- a/samples/AI眼镜配件/成品-评论/A款-防滑鼻托套装(2对装)_评论分析.xlsx
+++ b/samples/AI眼镜配件/成品-评论/A款-防滑鼻托套装(2对装)_评论分析.xlsx
@@ -1530,7 +1530,7 @@
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>安心感(夸)</t>
+          <t>戴稳踏实感(夸)</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>外观体面度(夸)</t>
+          <t>外观自然度(夸)</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr"/>
@@ -2670,7 +2670,7 @@
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>外观体面度(夸)</t>
+          <t>外观自然度(夸)</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr"/>
@@ -4166,7 +4166,7 @@
       <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr"/>
@@ -7410,7 +7410,7 @@
       <c r="S72" s="2" t="inlineStr"/>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>外观体面度</t>
+          <t>外观自然度</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr"/>
